--- a/data/google_news_dedup_audit_15_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_15_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,547 +445,337 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8331650495529175</v>
+        <v>0.7714263200759888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 8 Oxfordshire postcodes today — full list - Gloucestershire Live</t>
+          <t>Royal Mail delivery disruption hits 34 UK postcodes today as delays continue — full list - The Mirror</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays across UK today – full list of 36 affected postcodes - Daily Express</t>
+          <t>Royal Mail delivery delays hit 3 Nuneaton postcode areas today — full list - Coventry Telegraph</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7140761613845825</v>
+        <v>0.8448158502578735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 8 Oxfordshire postcodes today — full list - Gloucestershire Live</t>
+          <t>Winn-Dixie and Amazon expand grocery delivery to most of Florida - Lakeland Ledger</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Royal Mail delivery disruption alert for 36 UK postcodes today — check now - The Mirror</t>
+          <t>Amazon, Winn-Dixie Expand Florida Grocery Delivery - Store Brands</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="n">
         <v>9</v>
       </c>
-      <c r="B4" t="n">
-        <v>15</v>
-      </c>
       <c r="C4" t="n">
-        <v>0.7077566385269165</v>
+        <v>0.8488051891326904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>Winn-Dixie and Amazon expand grocery delivery to most of Florida - Lakeland Ledger</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Winn-Dixie teams with Amazon for same-day delivery in West Palm Beach - WFLX</t>
+          <t>Winn-Dixie and Amazon Expand Same-Day Grocery Delivery to West Palm Beach - National Today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7711608409881592</v>
+        <v>0.6518223285675049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Winn-Dixie Grocery Delivery by Amazon Now Covers Majority of Florida Households - Progressive Grocer</t>
+          <t>Patrick Bruel : une enquête ouverte à Bruxelles pour des faits présumés d’agression sexuelles - Anadolu Ajansı</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8125401735305786</v>
+        <v>0.7239440679550171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winn-Dixie and Amazon Expand Same-Day Grocery Delivery to West Palm Beach - National Today</t>
+          <t>“Tout le monde savait que Patrick Bruel était problématique” : une enquête ouverte en Belgique pour agression sexuelle - La Montagne</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7397933006286621</v>
+        <v>0.854658842086792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Amazon, Winn-Dixie expand sales and same-day delivery across Florida - Jacksonville Daily Record</t>
+          <t>La justice belge ouvre une enquête après une plainte pour agression sexuelle contre le chanteur Patrick Bruel - francebleu.fr</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8524179458618164</v>
+        <v>0.7271789908409119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Amazon expands online Winn-Dixie grocery delivery across Florida - Chain Store Age</t>
+          <t>Une enquête ouverte en Belgique visant Patrick Bruel pour agression sexuelle dans les locaux de la RTBF - BruxellesToday</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9090340137481689</v>
+        <v>0.692487359046936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Werknemer raakt gewond bij ontploffing in bedrijf in Deurne: “Na explosie volgde steekvlam” - HLN</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Werknemer raakt gewond bij ontploffing in bedrijf in Deurne: “Na explosie volgde steekvlam” | Foto - HLN</t>
+          <t>Patrick Bruel accusé d’agression sexuelle : la justice belge ouvre une enquête - parismatch.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7060166597366333</v>
+        <v>0.7234436869621277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Parket zet deur op een kier voor vervolging van politiemensen die betrokken waren bij dood van Sourour Abouda (46) - Nieuwsblad</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zaak-Sourour opnieuw uitgesteld, parket dagvaardt ook betrokken politiemensen - BRUZZ</t>
+          <t>Patrick Bruel accusé d'agressions sexuelles : la justice belge ouvre à son tour une enquête - Actu.fr</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9567897915840149</v>
+        <v>0.5781554579734802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nachtelijke explosie verwoest leegstaande woning in Roermond - De Limburger</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nachtelijke explosie verwoest ‘vermoedelijk leegstaande’ woning in Roermond - De Limburger</t>
+          <t>La justice belge enquête sur Bruel pour agression sexuelle - Watson</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7504564523696899</v>
+        <v>0.8424919247627258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nachtelijke explosie verwoest leegstaande woning in Roermond - De Limburger</t>
+          <t>EN DIRECT - Patrick Bruel : Au lendemain de l’ouverture d’une enquête en France, une autre enquête j... - jeanmarcmorandini.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grote ravage na explosie in ‘vermoedelijk leegstaand’ pand in Roermond - De Limburger</t>
+          <t>URGENT : Au lendemain de l’annonce de l’ouverture d’une enquête en France, une autre enquête judic... - jeanmarcmorandini.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7443652749061584</v>
+        <v>0.7665904760360718</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Un couteau sous la gorge et des coups de bâton: quatre jeunes arrêtés après avoir attaqué des mineurs - BruxellesToday</t>
+          <t>Two more men charged with Primrose Hill murder - BBC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Un carjacking sur la petite ceinture de Bruxelles fait un blessé - BruxellesToday</t>
+          <t>Two more charged with murder over 21-year-old’s Primrose Hill stabbing - London Now</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B14" t="n">
         <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6124610304832458</v>
+        <v>0.8344547748565674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Un couteau sous la gorge et des coups de bâton: quatre jeunes arrêtés après avoir attaqué des mineurs - BruxellesToday</t>
+          <t>Two more men charged with Primrose Hill murder - BBC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Patrick Bruel : après Bruxelles, une enquête pour tentative de viol ouverte à Paris - public.fr</t>
+          <t>Two more men charged with murder after Primrose Hill stabbing named - My London</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6327626705169678</v>
+        <v>0.7683069705963135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Un couteau sous la gorge et des coups de bâton: quatre jeunes arrêtés après avoir attaqué des mineurs - BruxellesToday</t>
+          <t>'Days of protests' set for Dartford Crossing and M25 due to rising fuel costs - London Now</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Une femme de 75 ans tuée dans un accident avec un camion près d'un magasin - BruxellesToday</t>
+          <t>Fuel protests set to hit London and M25 — everything you need to know - London Now</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9468143582344055</v>
+        <v>0.8468982577323914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Agressé alors qu’il rejoignait sa voiture: un homme blessé lors d’un carjacking à Bruxelles | Foto - 7sur7.be</t>
+          <t>'Days of protests' set for Dartford Crossing and M25 due to rising fuel costs - London Now</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Agressé alors qu’il rejoignait sa voiture: un homme blessé lors d’un carjacking à Bruxelles - 7sur7.be</t>
+          <t>LIVE updates as 'fuel protest' planned for Dartford Crossing and M25 - London Now</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7569339871406555</v>
+        <v>0.7080988883972168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cyclisme : Tour du Limbourg - tv.moustique.be</t>
+          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tour du Limbourg - Favoris, Parcours... tout savoir sur le Ronde van Limburg 2026 - Cyclism'Actu</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>54</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6842755079269409</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cyclisme : Tour du Limbourg - tv.moustique.be</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ronde van Limburg – Tour du Limbourg 2026 : parcours, favoris, engagés, TV direct - TodayCycling</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>61</v>
-      </c>
-      <c r="B19" t="n">
-        <v>62</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.662448525428772</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Lufthansa pilots to strike again for 2 more days - DW.com</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Hundreds of flights cancelled as Lufthansa strike enters 2nd day - Anadolu Ajansı</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>61</v>
-      </c>
-      <c r="B20" t="n">
-        <v>63</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7657442688941956</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Lufthansa pilots to strike again for 2 more days - DW.com</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Lufthansa strike: Hundreds more flights cancelled as another two-day walkout planned in major strike - The Independent</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>68</v>
-      </c>
-      <c r="B21" t="n">
-        <v>69</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6671557426452637</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nuevo tiroteo a plena luz del día en Barcelona: la víctima, en estado crítico, estaba en la terraza de un bar y los Mossos lo investigan como un posible ajuste de cuentas - El Mundo</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Un tiroteo deja un hombre gravemente herido en el barrio de Diagonal Mar de Barcelona - EL PAÍS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>68</v>
-      </c>
-      <c r="B22" t="n">
-        <v>71</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.6966360807418823</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nuevo tiroteo a plena luz del día en Barcelona: la víctima, en estado crítico, estaba en la terraza de un bar y los Mossos lo investigan como un posible ajuste de cuentas - El Mundo</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Un hombre herido crítico tras un tiroteo en una cafetería de Barcelona a plena luz del día - The Objective</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>68</v>
-      </c>
-      <c r="B23" t="n">
-        <v>72</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.7840707302093506</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nuevo tiroteo a plena luz del día en Barcelona: la víctima, en estado crítico, estaba en la terraza de un bar y los Mossos lo investigan como un posible ajuste de cuentas - El Mundo</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Herido crítico en un tiroteo a plena luz del día en Barcelona: tres hombres disparan cinco tiros y se escapan - El Caso</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>74</v>
-      </c>
-      <c r="B24" t="n">
-        <v>79</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.712563157081604</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Second man charged over Finbar Sullivan stabbing in Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Primrose Hill stabbing: Court remands man into custody - BBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>74</v>
-      </c>
-      <c r="B25" t="n">
-        <v>83</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.9527356028556824</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Second man charged over Finbar Sullivan stabbing in Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Second man charged in connection with Primrose Hill stabbing of Finbar Sullivan - Sky News</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>78</v>
-      </c>
-      <c r="B26" t="n">
-        <v>82</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.8139361143112183</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Fuel protests lead to key vote in Irish parliament - BBC</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Fuel protests have Ireland's government facing possible no-confidence vote - NPR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>85</v>
-      </c>
-      <c r="B27" t="n">
-        <v>88</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7240680456161499</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>London Tube drivers to strike twice this April over four-day week plans - London Now</t>
+          <t>Tube strike London— here are the lines affected and what to expect - London Now</t>
         </is>
       </c>
     </row>
